--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/100.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/100.xlsx
@@ -426,13 +426,13 @@
         <v>-8.82939193180524</v>
       </c>
       <c r="E2">
-        <v>-14.25374987919269</v>
+        <v>-15.05561582867889</v>
       </c>
       <c r="F2">
-        <v>-3.400757316780723</v>
+        <v>-3.772864095955275</v>
       </c>
       <c r="G2">
-        <v>-10.21795692053684</v>
+        <v>-9.399441088679737</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.325722150992398</v>
       </c>
       <c r="E3">
-        <v>-15.41313885158447</v>
+        <v>-15.71162868732605</v>
       </c>
       <c r="F3">
-        <v>-3.556723988114619</v>
+        <v>-3.829687614685112</v>
       </c>
       <c r="G3">
-        <v>-9.32911185924346</v>
+        <v>-9.450079193248429</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.745071836726582</v>
       </c>
       <c r="E4">
-        <v>-16.17757243492327</v>
+        <v>-15.79890143840188</v>
       </c>
       <c r="F4">
-        <v>-3.227698112457461</v>
+        <v>-3.904646580964439</v>
       </c>
       <c r="G4">
-        <v>-9.885723812397742</v>
+        <v>-9.006333669164519</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.140926243594091</v>
       </c>
       <c r="E5">
-        <v>-16.7842113414648</v>
+        <v>-16.87823604728606</v>
       </c>
       <c r="F5">
-        <v>-3.41182596201693</v>
+        <v>-3.729744259169949</v>
       </c>
       <c r="G5">
-        <v>-9.049480009177842</v>
+        <v>-9.021105323360748</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.516136632157081</v>
       </c>
       <c r="E6">
-        <v>-16.47428710885385</v>
+        <v>-17.9416032568192</v>
       </c>
       <c r="F6">
-        <v>-3.371865518505881</v>
+        <v>-3.588163844520472</v>
       </c>
       <c r="G6">
-        <v>-9.213242765368969</v>
+        <v>-8.684972392576388</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.883084602322367</v>
       </c>
       <c r="E7">
-        <v>-17.21745497825263</v>
+        <v>-18.75176989916146</v>
       </c>
       <c r="F7">
-        <v>-3.694925492128077</v>
+        <v>-3.897974909902292</v>
       </c>
       <c r="G7">
-        <v>-8.454048599030065</v>
+        <v>-8.287981703143604</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.244267976576934</v>
       </c>
       <c r="E8">
-        <v>-18.64454922008185</v>
+        <v>-18.62862257699688</v>
       </c>
       <c r="F8">
-        <v>-3.683142794190657</v>
+        <v>-3.726302392611317</v>
       </c>
       <c r="G8">
-        <v>-8.370609609258274</v>
+        <v>-7.999285579391461</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.612360988560103</v>
       </c>
       <c r="E9">
-        <v>-18.33151392582763</v>
+        <v>-19.81573939573762</v>
       </c>
       <c r="F9">
-        <v>-3.793314002028186</v>
+        <v>-3.978101232040283</v>
       </c>
       <c r="G9">
-        <v>-9.276815171359594</v>
+        <v>-8.026458537177799</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.985767493624043</v>
       </c>
       <c r="E10">
-        <v>-18.76894187259855</v>
+        <v>-19.82749984273554</v>
       </c>
       <c r="F10">
-        <v>-3.628792780525579</v>
+        <v>-4.048756001294664</v>
       </c>
       <c r="G10">
-        <v>-7.964829421418726</v>
+        <v>-6.903832681537703</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.377898814383295</v>
       </c>
       <c r="E11">
-        <v>-20.35535235849162</v>
+        <v>-20.94092933242348</v>
       </c>
       <c r="F11">
-        <v>-3.883652437507889</v>
+        <v>-3.813944492194908</v>
       </c>
       <c r="G11">
-        <v>-8.12275237527858</v>
+        <v>-7.456508396045792</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.798262084650254</v>
       </c>
       <c r="E12">
-        <v>-20.59519392735987</v>
+        <v>-21.89079034095435</v>
       </c>
       <c r="F12">
-        <v>-3.759851272424697</v>
+        <v>-4.003507260284143</v>
       </c>
       <c r="G12">
-        <v>-7.237307244254029</v>
+        <v>-6.947912595393099</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.252381152796588</v>
       </c>
       <c r="E13">
-        <v>-21.32001694855358</v>
+        <v>-21.94280892188046</v>
       </c>
       <c r="F13">
-        <v>-3.590475817941685</v>
+        <v>-3.888591992330782</v>
       </c>
       <c r="G13">
-        <v>-6.20227511303751</v>
+        <v>-6.295033288502349</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.758335160661909</v>
       </c>
       <c r="E14">
-        <v>-20.57021486473356</v>
+        <v>-23.00613084667352</v>
       </c>
       <c r="F14">
-        <v>-3.789330383188123</v>
+        <v>-3.41567869880735</v>
       </c>
       <c r="G14">
-        <v>-6.065708488451495</v>
+        <v>-5.992969181862629</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.321180688091517</v>
       </c>
       <c r="E15">
-        <v>-24.15041735824973</v>
+        <v>-23.23895780930389</v>
       </c>
       <c r="F15">
-        <v>-3.375121830766286</v>
+        <v>-3.317257054211129</v>
       </c>
       <c r="G15">
-        <v>-5.873753126447934</v>
+        <v>-5.346614960229783</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.9469034510140479</v>
       </c>
       <c r="E16">
-        <v>-23.51027227252544</v>
+        <v>-24.39613235790592</v>
       </c>
       <c r="F16">
-        <v>-2.999293196850956</v>
+        <v>-3.208470876671082</v>
       </c>
       <c r="G16">
-        <v>-5.392704375227516</v>
+        <v>-5.276077166424532</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.6401116611946117</v>
       </c>
       <c r="E17">
-        <v>-24.2234933433115</v>
+        <v>-24.88018547305981</v>
       </c>
       <c r="F17">
-        <v>-3.102576529734207</v>
+        <v>-3.250645546249813</v>
       </c>
       <c r="G17">
-        <v>-4.480344508968691</v>
+        <v>-4.98355736257453</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.3920049557258082</v>
       </c>
       <c r="E18">
-        <v>-23.94967463396371</v>
+        <v>-26.27546265651114</v>
       </c>
       <c r="F18">
-        <v>-2.837794688001165</v>
+        <v>-2.549824357561556</v>
       </c>
       <c r="G18">
-        <v>-5.534514903947737</v>
+        <v>-5.049761652268875</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.1964415908781106</v>
       </c>
       <c r="E19">
-        <v>-26.07750947221385</v>
+        <v>-26.66024256446888</v>
       </c>
       <c r="F19">
-        <v>-2.14288638583409</v>
+        <v>-2.641775624374509</v>
       </c>
       <c r="G19">
-        <v>-5.325993572065663</v>
+        <v>-5.262513861350137</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.0409968238120139</v>
       </c>
       <c r="E20">
-        <v>-26.84487297823561</v>
+        <v>-26.95107022218949</v>
       </c>
       <c r="F20">
-        <v>-2.200359344607723</v>
+        <v>-2.232959743744897</v>
       </c>
       <c r="G20">
-        <v>-4.551686765339985</v>
+        <v>-4.325371251184328</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.09079643004420881</v>
       </c>
       <c r="E21">
-        <v>-27.62770122299357</v>
+        <v>-28.33188798813433</v>
       </c>
       <c r="F21">
-        <v>-1.932134807948645</v>
+        <v>-2.038435054912892</v>
       </c>
       <c r="G21">
-        <v>-4.816553582300455</v>
+        <v>-4.166958336584663</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.2069162531582568</v>
       </c>
       <c r="E22">
-        <v>-28.10269286165811</v>
+        <v>-28.38566814544942</v>
       </c>
       <c r="F22">
-        <v>-1.779090616811825</v>
+        <v>-1.517666976529732</v>
       </c>
       <c r="G22">
-        <v>-4.297741438113571</v>
+        <v>-5.005890302782453</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.3165940860858105</v>
       </c>
       <c r="E23">
-        <v>-28.16090186655271</v>
+        <v>-28.05035275907746</v>
       </c>
       <c r="F23">
-        <v>-1.659490931195633</v>
+        <v>-1.019041158823404</v>
       </c>
       <c r="G23">
-        <v>-3.740490549670209</v>
+        <v>-4.015090370516137</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.4214002273619742</v>
       </c>
       <c r="E24">
-        <v>-28.42500247068005</v>
+        <v>-29.83153064780343</v>
       </c>
       <c r="F24">
-        <v>-1.738696937149113</v>
+        <v>-0.9966470744561218</v>
       </c>
       <c r="G24">
-        <v>-4.141205602834672</v>
+        <v>-4.933299970742854</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.5166259590897645</v>
       </c>
       <c r="E25">
-        <v>-29.22440040183207</v>
+        <v>-29.58310762069065</v>
       </c>
       <c r="F25">
-        <v>-1.206332543494163</v>
+        <v>-0.8066403014389851</v>
       </c>
       <c r="G25">
-        <v>-4.858375704098068</v>
+        <v>-4.438989174092115</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.5972444140700504</v>
       </c>
       <c r="E26">
-        <v>-29.98337490975463</v>
+        <v>-29.73175704422943</v>
       </c>
       <c r="F26">
-        <v>-1.106133222451535</v>
+        <v>-0.7872523623764627</v>
       </c>
       <c r="G26">
-        <v>-3.508341854274357</v>
+        <v>-4.509311782437314</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.6559557945776181</v>
       </c>
       <c r="E27">
-        <v>-28.88978240045729</v>
+        <v>-29.64479902209714</v>
       </c>
       <c r="F27">
-        <v>-0.5640860422252619</v>
+        <v>-0.2684475147379379</v>
       </c>
       <c r="G27">
-        <v>-5.086439186298461</v>
+        <v>-5.354414605520306</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.6878482473458456</v>
       </c>
       <c r="E28">
-        <v>-28.87086696452725</v>
+        <v>-29.73342125842725</v>
       </c>
       <c r="F28">
-        <v>-1.006814455958083</v>
+        <v>-0.8688540068588392</v>
       </c>
       <c r="G28">
-        <v>-5.10042955174742</v>
+        <v>-5.00149720885184</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6915797746844228</v>
       </c>
       <c r="E29">
-        <v>-30.27209456282466</v>
+        <v>-29.58646774840434</v>
       </c>
       <c r="F29">
-        <v>-0.9659278976907049</v>
+        <v>-0.8130195588079441</v>
       </c>
       <c r="G29">
-        <v>-4.915701110656088</v>
+        <v>-5.07830848645401</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.6679711978739661</v>
       </c>
       <c r="E30">
-        <v>-29.05467772449859</v>
+        <v>-29.15686726895568</v>
       </c>
       <c r="F30">
-        <v>-0.6180997387248036</v>
+        <v>-0.7914944318461989</v>
       </c>
       <c r="G30">
-        <v>-5.811362585214829</v>
+        <v>-5.482499612434708</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.6218592062601189</v>
       </c>
       <c r="E31">
-        <v>-28.89160737548238</v>
+        <v>-28.62522894892919</v>
       </c>
       <c r="F31">
-        <v>-0.5595797235540326</v>
+        <v>-0.7388384295198456</v>
       </c>
       <c r="G31">
-        <v>-5.296973329868411</v>
+        <v>-6.495003481256487</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.560529904604535</v>
       </c>
       <c r="E32">
-        <v>-28.33380806111358</v>
+        <v>-29.68127361599192</v>
       </c>
       <c r="F32">
-        <v>-0.8625683550063965</v>
+        <v>-0.5030022299428264</v>
       </c>
       <c r="G32">
-        <v>-5.47981144945682</v>
+        <v>-5.885144713648566</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.4929917889069123</v>
       </c>
       <c r="E33">
-        <v>-28.20558431958639</v>
+        <v>-27.81058364579334</v>
       </c>
       <c r="F33">
-        <v>-0.8865056878450939</v>
+        <v>-0.8155966097980534</v>
       </c>
       <c r="G33">
-        <v>-4.981094316693312</v>
+        <v>-5.999219491840773</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.4294287331443014</v>
       </c>
       <c r="E34">
-        <v>-28.73747623415731</v>
+        <v>-28.75590712336853</v>
       </c>
       <c r="F34">
-        <v>-1.419024157836964</v>
+        <v>-0.597750065107631</v>
       </c>
       <c r="G34">
-        <v>-5.3167405972834</v>
+        <v>-6.097671805633158</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.3787850466912153</v>
       </c>
       <c r="E35">
-        <v>-27.14531005780049</v>
+        <v>-28.13330987442397</v>
       </c>
       <c r="F35">
-        <v>-1.160916472268278</v>
+        <v>-0.7869698890921081</v>
       </c>
       <c r="G35">
-        <v>-5.797448362313272</v>
+        <v>-4.978167794436596</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3473112621405808</v>
       </c>
       <c r="E36">
-        <v>-28.32823803808414</v>
+        <v>-27.92402644815949</v>
       </c>
       <c r="F36">
-        <v>-1.29124517248553</v>
+        <v>-0.8697610691649047</v>
       </c>
       <c r="G36">
-        <v>-4.561234378675244</v>
+        <v>-6.154950864553628</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.3389938818107983</v>
       </c>
       <c r="E37">
-        <v>-26.82346235312735</v>
+        <v>-27.22505195660156</v>
       </c>
       <c r="F37">
-        <v>-1.298384871130258</v>
+        <v>-0.89241360416186</v>
       </c>
       <c r="G37">
-        <v>-5.35348434222377</v>
+        <v>-5.977300369825258</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3546694856755014</v>
       </c>
       <c r="E38">
-        <v>-25.37160188695017</v>
+        <v>-26.6696391480348</v>
       </c>
       <c r="F38">
-        <v>-1.20070958556396</v>
+        <v>-0.8018970696905552</v>
       </c>
       <c r="G38">
-        <v>-6.326354359849394</v>
+        <v>-5.152726239631287</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.391880436828176</v>
       </c>
       <c r="E39">
-        <v>-25.66154649223929</v>
+        <v>-27.09085968633227</v>
       </c>
       <c r="F39">
-        <v>-1.120243632790822</v>
+        <v>-0.6351864731423491</v>
       </c>
       <c r="G39">
-        <v>-5.182961452041451</v>
+        <v>-5.410531662956491</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4457563131400874</v>
       </c>
       <c r="E40">
-        <v>-24.43562517972681</v>
+        <v>-25.96251793173707</v>
       </c>
       <c r="F40">
-        <v>-1.08169058549713</v>
+        <v>-1.137929276840591</v>
       </c>
       <c r="G40">
-        <v>-5.058637224859661</v>
+        <v>-5.586877802742389</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.5097796027251729</v>
       </c>
       <c r="E41">
-        <v>-23.91514049118121</v>
+        <v>-25.0358064823334</v>
       </c>
       <c r="F41">
-        <v>-1.383391105638141</v>
+        <v>-1.123720290780371</v>
       </c>
       <c r="G41">
-        <v>-5.102660859440889</v>
+        <v>-5.249086288642854</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.5769583198087721</v>
       </c>
       <c r="E42">
-        <v>-24.63773097468914</v>
+        <v>-24.62171829059802</v>
       </c>
       <c r="F42">
-        <v>-1.325732592566281</v>
+        <v>-1.187338078947971</v>
       </c>
       <c r="G42">
-        <v>-4.386421021474028</v>
+        <v>-4.954242481824283</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.6401223019083171</v>
       </c>
       <c r="E43">
-        <v>-24.22677195849306</v>
+        <v>-24.47553462115641</v>
       </c>
       <c r="F43">
-        <v>-1.731882786893685</v>
+        <v>-1.081356753433802</v>
       </c>
       <c r="G43">
-        <v>-5.044689896502711</v>
+        <v>-4.729188285519089</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.6918562238852682</v>
       </c>
       <c r="E44">
-        <v>-23.97023843443254</v>
+        <v>-24.955865330676</v>
       </c>
       <c r="F44">
-        <v>-1.621434075976218</v>
+        <v>-1.545181199813718</v>
       </c>
       <c r="G44">
-        <v>-4.570848202921287</v>
+        <v>-4.835191953686552</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.7246370703255917</v>
       </c>
       <c r="E45">
-        <v>-21.7957059722153</v>
+        <v>-23.36962239832121</v>
       </c>
       <c r="F45">
-        <v>-1.421483580655876</v>
+        <v>-1.269179949977159</v>
       </c>
       <c r="G45">
-        <v>-4.039502333322722</v>
+        <v>-5.393075156327915</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.7329433265060353</v>
       </c>
       <c r="E46">
-        <v>-21.89100317923272</v>
+        <v>-22.63403972288528</v>
       </c>
       <c r="F46">
-        <v>-1.632400832021881</v>
+        <v>-1.457094266934824</v>
       </c>
       <c r="G46">
-        <v>-4.725986987982614</v>
+        <v>-4.283966258124663</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.7110991186269739</v>
       </c>
       <c r="E47">
-        <v>-20.38569313434301</v>
+        <v>-22.86710669463805</v>
       </c>
       <c r="F47">
-        <v>-1.365174478083177</v>
+        <v>-1.772268182882369</v>
       </c>
       <c r="G47">
-        <v>-4.678636255134418</v>
+        <v>-4.87826215115247</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.654453576857565</v>
       </c>
       <c r="E48">
-        <v>-21.97324932416003</v>
+        <v>-23.0968588234172</v>
       </c>
       <c r="F48">
-        <v>-1.158213509432943</v>
+        <v>-1.591222688428717</v>
       </c>
       <c r="G48">
-        <v>-5.236042739218125</v>
+        <v>-4.808849942830571</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.5616391110332656</v>
       </c>
       <c r="E49">
-        <v>-20.40614372296165</v>
+        <v>-21.33151474405905</v>
       </c>
       <c r="F49">
-        <v>-1.463044429989133</v>
+        <v>-1.717405409794958</v>
       </c>
       <c r="G49">
-        <v>-4.034546446650433</v>
+        <v>-4.647268836149823</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.4303480914753363</v>
       </c>
       <c r="E50">
-        <v>-19.51041609271846</v>
+        <v>-20.22481456674652</v>
       </c>
       <c r="F50">
-        <v>-1.362909721603923</v>
+        <v>-1.733387930464571</v>
       </c>
       <c r="G50">
-        <v>-5.590956394846772</v>
+        <v>-4.911973436378869</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.2621322029443038</v>
       </c>
       <c r="E51">
-        <v>-19.51979456238835</v>
+        <v>-20.87393961642801</v>
       </c>
       <c r="F51">
-        <v>-1.526182593430511</v>
+        <v>-1.584990052090054</v>
       </c>
       <c r="G51">
-        <v>-5.016791929243273</v>
+        <v>-4.980594424316882</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.05875390929908721</v>
       </c>
       <c r="E52">
-        <v>-17.96140627365474</v>
+        <v>-19.56919115686402</v>
       </c>
       <c r="F52">
-        <v>-1.283266337661765</v>
+        <v>-2.01646095281883</v>
       </c>
       <c r="G52">
-        <v>-4.769954343289674</v>
+        <v>-5.164955394853355</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1805787283960773</v>
       </c>
       <c r="E53">
-        <v>-17.57525423807267</v>
+        <v>-19.40094929053105</v>
       </c>
       <c r="F53">
-        <v>-1.759779715917763</v>
+        <v>-1.697396195180336</v>
       </c>
       <c r="G53">
-        <v>-5.948177500716289</v>
+        <v>-5.369699394275121</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.4515557521334455</v>
       </c>
       <c r="E54">
-        <v>-18.09865526387921</v>
+        <v>-18.97190807762233</v>
       </c>
       <c r="F54">
-        <v>-1.525034476210231</v>
+        <v>-1.847239574672738</v>
       </c>
       <c r="G54">
-        <v>-5.215656399787293</v>
+        <v>-5.209353121080521</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.7532661404661039</v>
       </c>
       <c r="E55">
-        <v>-17.44648255119056</v>
+        <v>-18.63880711504013</v>
       </c>
       <c r="F55">
-        <v>-1.601912769761845</v>
+        <v>-2.164678247099537</v>
       </c>
       <c r="G55">
-        <v>-5.078093300993958</v>
+        <v>-5.609783467328606</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.082584790421679</v>
       </c>
       <c r="E56">
-        <v>-16.13102877907243</v>
+        <v>-18.05832920284091</v>
       </c>
       <c r="F56">
-        <v>-1.498433113804131</v>
+        <v>-1.942953286229207</v>
       </c>
       <c r="G56">
-        <v>-5.410025149488983</v>
+        <v>-5.567653464795842</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.431173868169319</v>
       </c>
       <c r="E57">
-        <v>-16.4913232280707</v>
+        <v>-17.71461349718472</v>
       </c>
       <c r="F57">
-        <v>-1.841337456927792</v>
+        <v>-2.192383823253569</v>
       </c>
       <c r="G57">
-        <v>-6.307408107728145</v>
+        <v>-5.920223254182684</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.797152069746507</v>
       </c>
       <c r="E58">
-        <v>-16.07039704058374</v>
+        <v>-18.0709002466862</v>
       </c>
       <c r="F58">
-        <v>-1.452934205837965</v>
+        <v>-2.028768007322222</v>
       </c>
       <c r="G58">
-        <v>-5.994015314253038</v>
+        <v>-5.604241614095867</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.173705222564031</v>
       </c>
       <c r="E59">
-        <v>-15.06851292265274</v>
+        <v>-16.64446263358809</v>
       </c>
       <c r="F59">
-        <v>-1.695153804620957</v>
+        <v>-2.382862765690301</v>
       </c>
       <c r="G59">
-        <v>-6.328628704634873</v>
+        <v>-6.07173037078743</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.55425542859399</v>
       </c>
       <c r="E60">
-        <v>-15.78222306863163</v>
+        <v>-16.86352303523514</v>
       </c>
       <c r="F60">
-        <v>-2.082588694216911</v>
+        <v>-2.185973087923303</v>
       </c>
       <c r="G60">
-        <v>-6.741026673007425</v>
+        <v>-6.131353295949704</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.934321684835925</v>
       </c>
       <c r="E61">
-        <v>-14.97896687762507</v>
+        <v>-16.02064722513547</v>
       </c>
       <c r="F61">
-        <v>-1.782546565616305</v>
+        <v>-2.079446696658093</v>
       </c>
       <c r="G61">
-        <v>-7.018682127386099</v>
+        <v>-6.075974490168775</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.301322111583175</v>
       </c>
       <c r="E62">
-        <v>-14.88276397580612</v>
+        <v>-15.76239288095204</v>
       </c>
       <c r="F62">
-        <v>-1.965974444720408</v>
+        <v>-2.247938283122318</v>
       </c>
       <c r="G62">
-        <v>-7.061133252836173</v>
+        <v>-6.899790505434253</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.648428601785334</v>
       </c>
       <c r="E63">
-        <v>-15.2523372680461</v>
+        <v>-15.92195819108631</v>
       </c>
       <c r="F63">
-        <v>-2.256265032255258</v>
+        <v>-2.416810918591831</v>
       </c>
       <c r="G63">
-        <v>-7.251539279527356</v>
+        <v>-7.364594409693467</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.966696870357042</v>
       </c>
       <c r="E64">
-        <v>-14.82899287543904</v>
+        <v>-14.52423563167084</v>
       </c>
       <c r="F64">
-        <v>-1.837944464045925</v>
+        <v>-2.527363175434647</v>
       </c>
       <c r="G64">
-        <v>-6.658762926902074</v>
+        <v>-7.178588098023976</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.24443245334136</v>
       </c>
       <c r="E65">
-        <v>-13.32146387828558</v>
+        <v>-15.42762543993501</v>
       </c>
       <c r="F65">
-        <v>-1.811626403291582</v>
+        <v>-2.257646749083128</v>
       </c>
       <c r="G65">
-        <v>-7.670074999329715</v>
+        <v>-6.65101625034018</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.477307424131672</v>
       </c>
       <c r="E66">
-        <v>-13.95540495461935</v>
+        <v>-16.05882678949414</v>
       </c>
       <c r="F66">
-        <v>-2.380049629990394</v>
+        <v>-2.574513848001995</v>
       </c>
       <c r="G66">
-        <v>-6.723838320567529</v>
+        <v>-7.007518967827677</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.660047746342725</v>
       </c>
       <c r="E67">
-        <v>-13.55473010289468</v>
+        <v>-14.43605265731947</v>
       </c>
       <c r="F67">
-        <v>-2.313076953841457</v>
+        <v>-2.422867941041101</v>
       </c>
       <c r="G67">
-        <v>-7.296959964326157</v>
+        <v>-6.432328233107004</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.78958540883227</v>
       </c>
       <c r="E68">
-        <v>-13.84212064884347</v>
+        <v>-14.53158081651128</v>
       </c>
       <c r="F68">
-        <v>-2.553170133501463</v>
+        <v>-2.62882161492953</v>
       </c>
       <c r="G68">
-        <v>-8.519984734535729</v>
+        <v>-6.730591833467642</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.868759499331804</v>
       </c>
       <c r="E69">
-        <v>-13.15002490930319</v>
+        <v>-15.24593400579926</v>
       </c>
       <c r="F69">
-        <v>-2.122270806280619</v>
+        <v>-2.704249437158842</v>
       </c>
       <c r="G69">
-        <v>-6.539623014034784</v>
+        <v>-7.473067744833227</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.90004586347581</v>
       </c>
       <c r="E70">
-        <v>-13.06932750248651</v>
+        <v>-15.63653753133086</v>
       </c>
       <c r="F70">
-        <v>-2.142297416610699</v>
+        <v>-2.516956395753277</v>
       </c>
       <c r="G70">
-        <v>-8.13587537779625</v>
+        <v>-7.224273626465918</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.891288559483584</v>
       </c>
       <c r="E71">
-        <v>-12.1983842104873</v>
+        <v>-14.83720752728895</v>
       </c>
       <c r="F71">
-        <v>-2.570759686932508</v>
+        <v>-2.748494196877169</v>
       </c>
       <c r="G71">
-        <v>-8.316389494416089</v>
+        <v>-7.467519270509408</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.851498988036326</v>
       </c>
       <c r="E72">
-        <v>-13.67444484176146</v>
+        <v>-14.25231888140626</v>
       </c>
       <c r="F72">
-        <v>-2.254464989888975</v>
+        <v>-2.780633195370985</v>
       </c>
       <c r="G72">
-        <v>-7.425078076695951</v>
+        <v>-7.071488639283014</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.786034272150423</v>
       </c>
       <c r="E73">
-        <v>-13.48473348015812</v>
+        <v>-14.91336740314995</v>
       </c>
       <c r="F73">
-        <v>-2.960142896659846</v>
+        <v>-2.849683416966143</v>
       </c>
       <c r="G73">
-        <v>-7.645312118695967</v>
+        <v>-7.251996134811775</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.69957766469236</v>
       </c>
       <c r="E74">
-        <v>-14.52764104412461</v>
+        <v>-15.11582189061087</v>
       </c>
       <c r="F74">
-        <v>-2.356281284101868</v>
+        <v>-2.934208370012999</v>
       </c>
       <c r="G74">
-        <v>-7.234989862376539</v>
+        <v>-6.603586064399042</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.596555888950397</v>
       </c>
       <c r="E75">
-        <v>-14.15161467642369</v>
+        <v>-15.36780882676769</v>
       </c>
       <c r="F75">
-        <v>-2.639178692566733</v>
+        <v>-3.043267080428568</v>
       </c>
       <c r="G75">
-        <v>-6.290236308015945</v>
+        <v>-6.9884270517027</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.47686130449691</v>
       </c>
       <c r="E76">
-        <v>-14.60344769901301</v>
+        <v>-14.80261451434436</v>
       </c>
       <c r="F76">
-        <v>-2.44125769738325</v>
+        <v>-2.981284489514095</v>
       </c>
       <c r="G76">
-        <v>-7.69222254898744</v>
+        <v>-6.165531368097139</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.341654797834242</v>
       </c>
       <c r="E77">
-        <v>-14.563298248461</v>
+        <v>-16.03206350810881</v>
       </c>
       <c r="F77">
-        <v>-2.894891567973926</v>
+        <v>-3.442830097168909</v>
       </c>
       <c r="G77">
-        <v>-7.246927689591151</v>
+        <v>-6.563273551367336</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.192718938695722</v>
       </c>
       <c r="E78">
-        <v>-15.56844286767752</v>
+        <v>-16.05745919034382</v>
       </c>
       <c r="F78">
-        <v>-2.83970490323202</v>
+        <v>-3.06113413693955</v>
       </c>
       <c r="G78">
-        <v>-5.916055277348741</v>
+        <v>-5.726059758304428</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.031065520006213</v>
       </c>
       <c r="E79">
-        <v>-16.56105719931482</v>
+        <v>-16.83243506117248</v>
       </c>
       <c r="F79">
-        <v>-2.877643301912835</v>
+        <v>-3.275190900762165</v>
       </c>
       <c r="G79">
-        <v>-5.989304407950655</v>
+        <v>-5.75444437575814</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.861088311481811</v>
       </c>
       <c r="E80">
-        <v>-16.59198667678721</v>
+        <v>-17.03628884710177</v>
       </c>
       <c r="F80">
-        <v>-2.969535754640189</v>
+        <v>-3.541791837311755</v>
       </c>
       <c r="G80">
-        <v>-6.407062149551287</v>
+        <v>-6.325589623829822</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.684950305611545</v>
       </c>
       <c r="E81">
-        <v>-16.50945976647142</v>
+        <v>-18.60299141411346</v>
       </c>
       <c r="F81">
-        <v>-3.01020113881102</v>
+        <v>-3.138001661714928</v>
       </c>
       <c r="G81">
-        <v>-6.036767699347187</v>
+        <v>-5.643915191838492</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.504332677772033</v>
       </c>
       <c r="E82">
-        <v>-17.61923024916116</v>
+        <v>-18.50888066728606</v>
       </c>
       <c r="F82">
-        <v>-3.247720580950528</v>
+        <v>-3.213238959441596</v>
       </c>
       <c r="G82">
-        <v>-5.945896534839732</v>
+        <v>-5.570831588513542</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.326078417089806</v>
       </c>
       <c r="E83">
-        <v>-18.59072830650069</v>
+        <v>-19.75156639057493</v>
       </c>
       <c r="F83">
-        <v>-2.915815300201239</v>
+        <v>-3.467667037007047</v>
       </c>
       <c r="G83">
-        <v>-6.280562893950195</v>
+        <v>-5.060815563824502</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.154416119532621</v>
       </c>
       <c r="E84">
-        <v>-20.81069947691089</v>
+        <v>-20.17750559878838</v>
       </c>
       <c r="F84">
-        <v>-3.618221155731052</v>
+        <v>-3.704215632550474</v>
       </c>
       <c r="G84">
-        <v>-5.900916152597654</v>
+        <v>-4.70001906877257</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.997108535715715</v>
       </c>
       <c r="E85">
-        <v>-19.45776805390529</v>
+        <v>-21.756561842893</v>
       </c>
       <c r="F85">
-        <v>-3.264948966193952</v>
+        <v>-3.567408270875927</v>
       </c>
       <c r="G85">
-        <v>-5.807320409111379</v>
+        <v>-5.272438876876873</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.860897587011225</v>
       </c>
       <c r="E86">
-        <v>-21.22938859823807</v>
+        <v>-22.754909222624</v>
       </c>
       <c r="F86">
-        <v>-2.695675834539867</v>
+        <v>-3.941818739797665</v>
       </c>
       <c r="G86">
-        <v>-4.892951041710217</v>
+        <v>-5.011303044739162</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.752637478178705</v>
       </c>
       <c r="E87">
-        <v>-21.61925851098043</v>
+        <v>-23.06231109521269</v>
       </c>
       <c r="F87">
-        <v>-3.62849125479096</v>
+        <v>-3.563060170378633</v>
       </c>
       <c r="G87">
-        <v>-5.339987248060162</v>
+        <v>-4.530459547342178</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.682402145009219</v>
       </c>
       <c r="E88">
-        <v>-23.16658826618731</v>
+        <v>-25.57033396877679</v>
       </c>
       <c r="F88">
-        <v>-3.466366500184652</v>
+        <v>-3.661516606405771</v>
       </c>
       <c r="G88">
-        <v>-4.745628454667109</v>
+        <v>-4.517555040830099</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.656564698336126</v>
       </c>
       <c r="E89">
-        <v>-25.08565139573583</v>
+        <v>-25.38290042959931</v>
       </c>
       <c r="F89">
-        <v>-3.270535475958432</v>
+        <v>-3.829830093878394</v>
       </c>
       <c r="G89">
-        <v>-5.552451439679508</v>
+        <v>-4.81439510660885</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.681737319300595</v>
       </c>
       <c r="E90">
-        <v>-25.62036002113952</v>
+        <v>-28.04767190246492</v>
       </c>
       <c r="F90">
-        <v>-3.674206366649256</v>
+        <v>-3.849004314150994</v>
       </c>
       <c r="G90">
-        <v>-4.380948689697613</v>
+        <v>-3.728966540648006</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.763053835830025</v>
       </c>
       <c r="E91">
-        <v>-26.51625520492099</v>
+        <v>-28.84902613438826</v>
       </c>
       <c r="F91">
-        <v>-3.30736220558469</v>
+        <v>-4.021623655383369</v>
       </c>
       <c r="G91">
-        <v>-4.79409484136204</v>
+        <v>-5.465655556730896</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.901034145978048</v>
       </c>
       <c r="E92">
-        <v>-29.33375399216929</v>
+        <v>-30.1987921540625</v>
       </c>
       <c r="F92">
-        <v>-3.376260835945136</v>
+        <v>-4.076354718053735</v>
       </c>
       <c r="G92">
-        <v>-4.532786860856286</v>
+        <v>-5.000100158634267</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.096915750423039</v>
       </c>
       <c r="E93">
-        <v>-30.43490678882243</v>
+        <v>-32.30401179311833</v>
       </c>
       <c r="F93">
-        <v>-3.605235668324767</v>
+        <v>-4.179775559925851</v>
       </c>
       <c r="G93">
-        <v>-5.236211577040628</v>
+        <v>-5.213339017909803</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.342736336275193</v>
       </c>
       <c r="E94">
-        <v>-32.60929886834543</v>
+        <v>-34.6180099335868</v>
       </c>
       <c r="F94">
-        <v>-4.10184772487489</v>
+        <v>-4.147545441017727</v>
       </c>
       <c r="G94">
-        <v>-5.471293415784275</v>
+        <v>-5.195680568003331</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.630522716655558</v>
       </c>
       <c r="E95">
-        <v>-34.96587145719701</v>
+        <v>-36.58982299261367</v>
       </c>
       <c r="F95">
-        <v>-3.770427039056238</v>
+        <v>-4.393090106555556</v>
       </c>
       <c r="G95">
-        <v>-6.032626206877558</v>
+        <v>-5.56629945167028</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.950387592477868</v>
       </c>
       <c r="E96">
-        <v>-37.12389763165628</v>
+        <v>-37.71794285198249</v>
       </c>
       <c r="F96">
-        <v>-3.987544620432197</v>
+        <v>-4.064957210958617</v>
       </c>
       <c r="G96">
-        <v>-5.686823172572987</v>
+        <v>-5.960873442859395</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.282857087030044</v>
       </c>
       <c r="E97">
-        <v>-38.33535046971426</v>
+        <v>-40.18848807465911</v>
       </c>
       <c r="F97">
-        <v>-4.339778037246186</v>
+        <v>-4.271022714446424</v>
       </c>
       <c r="G97">
-        <v>-5.344512763812346</v>
+        <v>-6.034834340752252</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.619376189617559</v>
       </c>
       <c r="E98">
-        <v>-40.40852662669181</v>
+        <v>-42.84101228957097</v>
       </c>
       <c r="F98">
-        <v>-4.253390914277837</v>
+        <v>-4.146525720744881</v>
       </c>
       <c r="G98">
-        <v>-6.69589731621608</v>
+        <v>-6.870084980310373</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.938634396730296</v>
       </c>
       <c r="E99">
-        <v>-42.66215794440102</v>
+        <v>-44.45627141912991</v>
       </c>
       <c r="F99">
-        <v>-4.653658043310558</v>
+        <v>-4.380713469190329</v>
       </c>
       <c r="G99">
-        <v>-7.705325688231875</v>
+        <v>-7.267088911925312</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.240079156290379</v>
       </c>
       <c r="E100">
-        <v>-44.63399364579794</v>
+        <v>-45.72489624153472</v>
       </c>
       <c r="F100">
-        <v>-4.303491403166554</v>
+        <v>-4.708116573105403</v>
       </c>
       <c r="G100">
-        <v>-7.43657560135384</v>
+        <v>-7.313108805466721</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.499805417446177</v>
       </c>
       <c r="E101">
-        <v>-47.16752767768425</v>
+        <v>-48.3432485915847</v>
       </c>
       <c r="F101">
-        <v>-4.771165272867279</v>
+        <v>-4.653109664089905</v>
       </c>
       <c r="G101">
-        <v>-7.156341232000074</v>
+        <v>-7.311655475974981</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.739500450283346</v>
       </c>
       <c r="E102">
-        <v>-50.14888023995208</v>
+        <v>-50.1266318471524</v>
       </c>
       <c r="F102">
-        <v>-4.696158261278589</v>
+        <v>-4.471366684283096</v>
       </c>
       <c r="G102">
-        <v>-6.968629989377858</v>
+        <v>-7.596521298538188</v>
       </c>
     </row>
   </sheetData>
